--- a/tabular/reference/sublineage/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_ltr_data_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E718781-1669-9441-9C65-B3D6545FB97C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D1447B-9273-664F-985A-74887C1564E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="500" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6940" yWindow="500" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ltr_lineage_table" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="86">
   <si>
     <t>LTR_name</t>
   </si>
@@ -193,12 +193,6 @@
     <t>MLT2C1</t>
   </si>
   <si>
-    <t>MER74C</t>
-  </si>
-  <si>
-    <t>HERVL74</t>
-  </si>
-  <si>
     <t>LTR53</t>
   </si>
   <si>
@@ -307,16 +301,16 @@
     <t>ERV-3.Lambda.Lb4</t>
   </si>
   <si>
-    <t>ERV-3.Lambda.74</t>
-  </si>
-  <si>
-    <t>LTR47B2</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.47</t>
-  </si>
-  <si>
-    <t>ERV-L47</t>
+    <t>HARLEQUIN_LTR</t>
+  </si>
+  <si>
+    <t>ERV-1.Eta.E.HQ</t>
+  </si>
+  <si>
+    <t>HARLEQUIN</t>
+  </si>
+  <si>
+    <t>Eta</t>
   </si>
 </sst>
 </file>
@@ -890,7 +884,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1251,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1271,16 +1275,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -1289,57 +1293,53 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="I2" t="str">
-        <f t="shared" ref="I2:I23" si="0">IF(A2&lt;&gt;B2,"FLAG","")</f>
-        <v/>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>9</v>
@@ -1348,28 +1348,28 @@
         <v>4</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I3:I25" si="0">IF(A3&lt;&gt;B3,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>9</v>
@@ -1384,22 +1384,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>9</v>
@@ -1414,22 +1414,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>9</v>
@@ -1444,22 +1444,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>9</v>
@@ -1474,22 +1474,22 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>9</v>
@@ -1504,22 +1504,22 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>9</v>
@@ -1534,22 +1534,22 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>9</v>
@@ -1564,22 +1564,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>9</v>
@@ -1594,22 +1594,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>9</v>
@@ -1624,22 +1624,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>9</v>
@@ -1654,22 +1654,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>9</v>
@@ -1684,22 +1684,22 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>9</v>
@@ -1714,22 +1714,22 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>9</v>
@@ -1744,22 +1744,22 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>9</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>9</v>
@@ -1804,22 +1804,22 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>9</v>
@@ -1834,22 +1834,22 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>9</v>
@@ -1864,22 +1864,22 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>9</v>
@@ -1894,22 +1894,22 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>9</v>
@@ -1924,22 +1924,22 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>9</v>
@@ -1954,52 +1954,52 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="E24" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" ref="I24:I25" si="1">IF(A24&lt;&gt;B24,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>39</v>
@@ -2008,48 +2008,37 @@
         <v>4</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I26">
-    <sortCondition ref="C3:C26"/>
-    <sortCondition ref="G3:G26"/>
-    <sortCondition ref="H3:H26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I25">
+    <sortCondition ref="C2:C25"/>
+    <sortCondition ref="G2:G25"/>
+    <sortCondition ref="H2:H25"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="containsText" dxfId="4" priority="49" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="5" priority="51" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="50">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I25)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2077,16 +2066,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -2095,18 +2084,18 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -2130,13 +2119,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -2160,13 +2149,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -2190,13 +2179,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -2220,13 +2209,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -2250,13 +2239,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -2280,13 +2269,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -2310,13 +2299,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
@@ -2340,13 +2329,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -2370,13 +2359,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -2400,13 +2389,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -2430,13 +2419,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
@@ -2460,13 +2449,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -2496,7 +2485,7 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
@@ -2520,13 +2509,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -2546,13 +2535,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
@@ -2578,7 +2567,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
@@ -2608,7 +2597,7 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
@@ -2638,7 +2627,7 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
@@ -2668,7 +2657,7 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
@@ -2698,16 +2687,16 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
         <v>6</v>
@@ -2728,7 +2717,7 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
         <v>39</v>
@@ -2737,7 +2726,7 @@
         <v>39</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G23" t="s">
         <v>39</v>
@@ -2752,22 +2741,22 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
         <v>39</v>
@@ -2782,22 +2771,22 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G25" t="s">
         <v>39</v>
@@ -2818,16 +2807,16 @@
         <v>38</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>39</v>
@@ -2848,16 +2837,16 @@
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>39</v>

--- a/tabular/reference/sublineage/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D1447B-9273-664F-985A-74887C1564E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9727F1-5352-0045-B61C-2B0841CE0AE9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6940" yWindow="500" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="97">
   <si>
     <t>LTR_name</t>
   </si>
@@ -311,6 +311,39 @@
   </si>
   <si>
     <t>Eta</t>
+  </si>
+  <si>
+    <t>reference_role</t>
+  </si>
+  <si>
+    <t>reference_status</t>
+  </si>
+  <si>
+    <t>derivation_method</t>
+  </si>
+  <si>
+    <t>derivation_source</t>
+  </si>
+  <si>
+    <t>num_input_sequences</t>
+  </si>
+  <si>
+    <t>dfam_accession</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>canonical</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>consensus</t>
+  </si>
+  <si>
+    <t>repbase</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1267,7 +1300,7 @@
     <col min="8" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1293,10 +1326,28 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>82</v>
       </c>
@@ -1321,8 +1372,20 @@
       <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -1347,12 +1410,20 @@
       <c r="H3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I3" t="str">
-        <f t="shared" ref="I3:I25" si="0">IF(A3&lt;&gt;B3,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
@@ -1377,12 +1448,20 @@
       <c r="H4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -1407,12 +1486,20 @@
       <c r="H5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
@@ -1437,12 +1524,20 @@
       <c r="H6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I6" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -1467,12 +1562,20 @@
       <c r="H7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I7" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1497,12 +1600,20 @@
       <c r="H8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
@@ -1527,12 +1638,20 @@
       <c r="H9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" t="s">
+        <v>95</v>
+      </c>
+      <c r="L9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
@@ -1557,12 +1676,20 @@
       <c r="H10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" t="s">
+        <v>94</v>
+      </c>
+      <c r="K10" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
@@ -1587,12 +1714,20 @@
       <c r="H11" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1617,12 +1752,20 @@
       <c r="H12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" t="s">
+        <v>94</v>
+      </c>
+      <c r="K12" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
@@ -1647,12 +1790,20 @@
       <c r="H13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I13" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" t="s">
+        <v>95</v>
+      </c>
+      <c r="L13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>25</v>
       </c>
@@ -1677,12 +1828,20 @@
       <c r="H14" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" t="s">
+        <v>94</v>
+      </c>
+      <c r="K14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>26</v>
       </c>
@@ -1707,12 +1866,20 @@
       <c r="H15" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" t="s">
+        <v>94</v>
+      </c>
+      <c r="K15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>27</v>
       </c>
@@ -1737,12 +1904,20 @@
       <c r="H16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K16" t="s">
+        <v>95</v>
+      </c>
+      <c r="L16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
@@ -1767,12 +1942,20 @@
       <c r="H17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I17" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17" t="s">
+        <v>95</v>
+      </c>
+      <c r="L17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>29</v>
       </c>
@@ -1797,12 +1980,20 @@
       <c r="H18" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I18" t="s">
+        <v>93</v>
+      </c>
+      <c r="J18" t="s">
+        <v>94</v>
+      </c>
+      <c r="K18" t="s">
+        <v>95</v>
+      </c>
+      <c r="L18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>30</v>
       </c>
@@ -1827,12 +2018,20 @@
       <c r="H19" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I19" t="s">
+        <v>93</v>
+      </c>
+      <c r="J19" t="s">
+        <v>94</v>
+      </c>
+      <c r="K19" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>31</v>
       </c>
@@ -1857,12 +2056,20 @@
       <c r="H20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I20" t="s">
+        <v>93</v>
+      </c>
+      <c r="J20" t="s">
+        <v>94</v>
+      </c>
+      <c r="K20" t="s">
+        <v>95</v>
+      </c>
+      <c r="L20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>32</v>
       </c>
@@ -1887,12 +2094,20 @@
       <c r="H21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I21" t="s">
+        <v>93</v>
+      </c>
+      <c r="J21" t="s">
+        <v>94</v>
+      </c>
+      <c r="K21" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>33</v>
       </c>
@@ -1917,12 +2132,20 @@
       <c r="H22" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I22" t="s">
+        <v>93</v>
+      </c>
+      <c r="J22" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" t="s">
+        <v>95</v>
+      </c>
+      <c r="L22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>34</v>
       </c>
@@ -1947,12 +2170,20 @@
       <c r="H23" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I23" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>35</v>
       </c>
@@ -1977,12 +2208,20 @@
       <c r="H24" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I24" t="s">
+        <v>93</v>
+      </c>
+      <c r="J24" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" t="s">
+        <v>95</v>
+      </c>
+      <c r="L24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
@@ -2007,9 +2246,17 @@
       <c r="H25" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="I25" t="s">
+        <v>93</v>
+      </c>
+      <c r="J25" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" t="s">
+        <v>95</v>
+      </c>
+      <c r="L25" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2019,36 +2266,6 @@
     <sortCondition ref="H2:H25"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="I2:I24">
-    <cfRule type="containsText" dxfId="5" priority="51" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I25">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I25)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
